--- a/data/raw/prosandcons.xlsx
+++ b/data/raw/prosandcons.xlsx
@@ -1,15 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pros &amp; Cons" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pros &amp; Cons'!$A$2:$D$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +27,47 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +75,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,72 +478,369 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bluestock Fintech — Nifty 100  |  Pros &amp; Cons  |  16 records</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>pros</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>cons</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="3">
+      <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Growth</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Debt</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Company is expected to give good quarter</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Stock is trading at 2.76 times its book value</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Stable</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Competition</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Company has delivered good profit growth of 23.4% CAGR over last 5 years</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Company has low interest coverage ratio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Leader</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>High PE</t>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Company has been maintaining a healthy dividend payout of 22.9%</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Contingent liabilities of Rs.24,09,821 Cr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Company's median sales growth is 16.4% of last 10 years</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Earnings include an other income of Rs.1,55,870 Cr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Company is almost debt free.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Stock is trading at 9.11 times its book value</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Company is expected to give good quarter</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Tax rate seems low</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Company has a low return on equity of 12.9% over last 3 years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Earnings include an other income of Rs.1,657 Cr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Dividend payout has been low at 14.0% of profits over last 3 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Company has a good return on equity (ROE) track record: 3 Years ROE 30.9%</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Stock is trading at 9.03 times its book value</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Company has been maintaining a healthy dividend payout of 63.3%</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Promoter holding is low: 14.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>The company has delivered a poor sales growth of 8.75% over past five years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Dividend payout has been low at 12.2% of profits over last 3 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Company is almost debt free.</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Stock is trading at 15.2 times its book value</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Company has a good return on equity (ROE) track record: 3 Years ROE 47.4%</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>The company has delivered a poor sales growth of 10.5% over past five years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Company has been maintaining a healthy dividend payout of 66.2%</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:D2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>